--- a/data/experimental/mlb-props/mlb_props_2026-05-04.xlsx
+++ b/data/experimental/mlb-props/mlb_props_2026-05-04.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,32 +652,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Tyler Holton</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>43.33333333333334</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="F6" t="n">
         <v>0.92</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53</v>
+        <v>2.29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2806</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1467</v>
+        <v>0.0297</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0678</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.028</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="7">
@@ -688,78 +688,78 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0789</v>
+        <v>0.0771</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0277</v>
+        <v>0.027</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0023</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PHI@MIA</t>
+          <t>TOR@TB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>31.33333333333333</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="G8" t="n">
-        <v>3.19</v>
+        <v>2.26</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2171</v>
+        <v>0.0789</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1039</v>
+        <v>0.0277</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0438</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0165</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="9">
@@ -770,78 +770,78 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>31.33333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="G9" t="n">
-        <v>2.03</v>
+        <v>3.19</v>
       </c>
       <c r="H9" t="n">
-        <v>0.055</v>
+        <v>0.2171</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0175</v>
+        <v>0.1039</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0049</v>
+        <v>0.0438</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0012</v>
+        <v>0.0165</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BAL@NYY</t>
+          <t>PHI@MIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shane Baz</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.03</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1406</v>
+        <v>0.055</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0586</v>
+        <v>0.0175</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0214</v>
+        <v>0.0049</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="11">
@@ -852,43 +852,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Shane Baz</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
-        <v>41.66666666666666</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="G11" t="n">
-        <v>3.84</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3403</v>
+        <v>0.1406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1906</v>
+        <v>0.0586</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0948</v>
+        <v>0.0214</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0423</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CIN@CHC</t>
+          <t>BAL@NYY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -898,73 +898,73 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E12" t="n">
-        <v>35.33333333333334</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="G12" t="n">
-        <v>2.76</v>
+        <v>3.84</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1459</v>
+        <v>0.3403</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0615</v>
+        <v>0.1906</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0228</v>
+        <v>0.0948</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0075</v>
+        <v>0.0423</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CLE@KC</t>
+          <t>CIN@CHC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
         <v>35.33333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1158</v>
+        <v>0.1459</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0456</v>
+        <v>0.0615</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0157</v>
+        <v>0.0228</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0048</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="14">
@@ -975,78 +975,78 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>37.33333333333334</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1933</v>
+        <v>0.1158</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0891</v>
+        <v>0.0456</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0361</v>
+        <v>0.0157</v>
       </c>
       <c r="K14" t="n">
-        <v>0.013</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIL@STL</t>
+          <t>CLE@KC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chad Patrick</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="G15" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0901</v>
+        <v>0.1933</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0329</v>
+        <v>0.0891</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0105</v>
+        <v>0.0361</v>
       </c>
       <c r="K15" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="16">
@@ -1057,78 +1057,78 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kyle Leahy</t>
+          <t>Chad Patrick</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>29.33333333333333</v>
+        <v>28</v>
       </c>
       <c r="F16" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="G16" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0589</v>
+        <v>0.0901</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0191</v>
+        <v>0.0329</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0013</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LAD@HOU</t>
+          <t>MIL@STL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Kyle Leahy</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>37.66666666666666</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="F17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G17" t="n">
-        <v>2.95</v>
+        <v>2.07</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1772</v>
+        <v>0.0589</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0794</v>
+        <v>0.0191</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0313</v>
+        <v>0.0054</v>
       </c>
       <c r="K17" t="n">
-        <v>0.011</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="18">
@@ -1139,78 +1139,78 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steven Okert</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>37.66666666666666</v>
       </c>
       <c r="F18" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0619</v>
+        <v>0.1772</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0204</v>
+        <v>0.0794</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0058</v>
+        <v>0.0313</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0015</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CWS@LAA</t>
+          <t>LAD@HOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Steven Okert</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>1.08</v>
+        <v>0.87</v>
       </c>
       <c r="G19" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2053</v>
+        <v>0.0619</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0965</v>
+        <v>0.0204</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0399</v>
+        <v>0.0058</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0147</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="20">
@@ -1221,78 +1221,78 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E20" t="n">
-        <v>42.66666666666666</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G20" t="n">
-        <v>3.85</v>
+        <v>3.12</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3422</v>
+        <v>0.2053</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1921</v>
+        <v>0.0965</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0958</v>
+        <v>0.0399</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0428</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ATL@SEA</t>
+          <t>CWS@LAA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JR Ritchie</t>
+          <t>José Soriano</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E21" t="n">
-        <v>12.33333333333333</v>
+        <v>42.66666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>2.76</v>
+        <v>3.85</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1469</v>
+        <v>0.3422</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0621</v>
+        <v>0.1921</v>
       </c>
       <c r="J21" t="n">
-        <v>0.023</v>
+        <v>0.0958</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0076</v>
+        <v>0.0428</v>
       </c>
     </row>
     <row r="22">
@@ -1303,77 +1303,118 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>JR Ritchie</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>38</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.83</v>
+        <v>1.02</v>
       </c>
       <c r="G22" t="n">
-        <v>3.04</v>
+        <v>2.76</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1907</v>
+        <v>0.1469</v>
       </c>
       <c r="I22" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0621</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0353</v>
+        <v>0.023</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0127</v>
+        <v>0.0076</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>ATL@SEA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Logan Gilbert</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>39</v>
+      </c>
+      <c r="E23" t="n">
+        <v>38</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1907</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0127</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>SD@SF</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Randy Vásquez</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D24" t="n">
         <v>34</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>33.66666666666666</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>0.92</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>3.12</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>0.2053</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>0.0965</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>0.0399</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -1391,7 +1432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2113,6 +2154,3210 @@
         <v>0.1061</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>680776</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="F21" t="n">
+        <v>113</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6728</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2511</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>575929</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F22" t="n">
+        <v>118</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8393</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4669</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>701350</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="F23" t="n">
+        <v>108</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7635</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.353</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>596115</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="F24" t="n">
+        <v>130</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7199</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3002</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>677800</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="F25" t="n">
+        <v>124</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.562</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8619</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5082</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>678882</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="F26" t="n">
+        <v>106</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4088</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>691785</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="F27" t="n">
+        <v>86</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7858000000000001</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3832</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>665966</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="F28" t="n">
+        <v>70</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7131</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.2826</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>655316</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="F29" t="n">
+        <v>46</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.2587</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>663330</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="F30" t="n">
+        <v>38</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4518</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>663837</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="F31" t="n">
+        <v>70</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4568</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.0987</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>693307</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="F32" t="n">
+        <v>101</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.1365</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>682985</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F33" t="n">
+        <v>124</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5733</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.1683</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>679529</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="F34" t="n">
+        <v>111</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.1079</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>672761</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="F35" t="n">
+        <v>56</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.0587</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>701678</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="F36" t="n">
+        <v>33</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.4534</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.097</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>690993</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="F37" t="n">
+        <v>99</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5558999999999999</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.1502</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>670097</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0968</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>682818</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.6026</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1901</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>672960</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="F40" t="n">
+        <v>123</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.5872000000000001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.1784</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>665489</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F41" t="n">
+        <v>126</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7312</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.3132</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>660821</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F42" t="n">
+        <v>104</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.1967</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>676391</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="F43" t="n">
+        <v>134</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6745</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.2528</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>662139</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="F44" t="n">
+        <v>111</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>664702</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="F45" t="n">
+        <v>51</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6788</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.257</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>665926</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="F46" t="n">
+        <v>112</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.5767</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.1642</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" t="n">
+        <v>678218</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="F47" t="n">
+        <v>44</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.4843</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.1083</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>802415</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F48" t="n">
+        <v>130</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7872</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.3852</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>691406</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="F49" t="n">
+        <v>125</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7347</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.3173</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>668723</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F50" t="n">
+        <v>40</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.7517</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.3379</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>650490</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F51" t="n">
+        <v>117</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.8280999999999999</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.4478</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>666018</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="F52" t="n">
+        <v>119</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.7151999999999999</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.295</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>676356</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="F53" t="n">
+        <v>68</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.3454</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>810938</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="F54" t="n">
+        <v>86</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.7016</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.2803</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" t="n">
+        <v>663743</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="F55" t="n">
+        <v>84</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.6836</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.2525</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>9</v>
+      </c>
+      <c r="D56" t="n">
+        <v>670764</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="F56" t="n">
+        <v>68</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.5505</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1467</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>607208</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="F57" t="n">
+        <v>136</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.6264</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.2094</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>656941</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F58" t="n">
+        <v>123</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.177</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="n">
+        <v>547180</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="F59" t="n">
+        <v>125</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.6482</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.2283</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>666969</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="F60" t="n">
+        <v>119</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.198</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>669016</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="F61" t="n">
+        <v>106</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.7302</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.3119</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>681082</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="F62" t="n">
+        <v>97</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.5588</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.1582</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" t="n">
+        <v>664761</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="F63" t="n">
+        <v>117</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>596117</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="F64" t="n">
+        <v>11</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.1671</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>9</v>
+      </c>
+      <c r="D65" t="n">
+        <v>702222</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="F65" t="n">
+        <v>97</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.1952</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>805300</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F66" t="n">
+        <v>126</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.5991</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.1874</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>669065</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="F67" t="n">
+        <v>46</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.6891</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.2673</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="n">
+        <v>672640</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="F68" t="n">
+        <v>132</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.592</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.8687</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.5215</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="n">
+        <v>669364</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F69" t="n">
+        <v>125</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.569</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.8636</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.5113</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>689414</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="F70" t="n">
+        <v>97</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.456</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" t="n">
+        <v>666624</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.7401</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.3237</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>8</v>
+      </c>
+      <c r="D72" t="n">
+        <v>683357</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="F72" t="n">
+        <v>92</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.6202</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.1966</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9</v>
+      </c>
+      <c r="D73" t="n">
+        <v>688363</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="F73" t="n">
+        <v>70</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.5755</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.1634</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>683002</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F74" t="n">
+        <v>139</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.4614</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.101</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
+        <v>668939</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="F75" t="n">
+        <v>71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.1854</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" t="n">
+        <v>687637</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="F76" t="n">
+        <v>83</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>624413</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="F77" t="n">
+        <v>126</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.1053</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>694212</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="F78" t="n">
+        <v>90</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.1328</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>6</v>
+      </c>
+      <c r="D79" t="n">
+        <v>665750</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="F79" t="n">
+        <v>72</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.1666</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>7</v>
+      </c>
+      <c r="D80" t="n">
+        <v>681297</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="F80" t="n">
+        <v>60</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.0794</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" t="n">
+        <v>669236</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="F81" t="n">
+        <v>108</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.4956</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.1143</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" t="n">
+        <v>677942</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="F82" t="n">
+        <v>73</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>663757</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="F83" t="n">
+        <v>105</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.5884</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.1793</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>592450</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="F84" t="n">
+        <v>121</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.7916</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3914</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>641355</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F85" t="n">
+        <v>120</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.8078</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.4154</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>4</v>
+      </c>
+      <c r="D86" t="n">
+        <v>691176</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="F86" t="n">
+        <v>18</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.7613</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.3501</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>5</v>
+      </c>
+      <c r="D87" t="n">
+        <v>665862</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="F87" t="n">
+        <v>118</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.7009</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.2795</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>6</v>
+      </c>
+      <c r="D88" t="n">
+        <v>502671</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="F88" t="n">
+        <v>35</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.6107</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.1965</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>7</v>
+      </c>
+      <c r="D89" t="n">
+        <v>669224</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="F89" t="n">
+        <v>79</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.6826</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.2607</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" t="n">
+        <v>641857</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F90" t="n">
+        <v>80</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.2023</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>9</v>
+      </c>
+      <c r="D91" t="n">
+        <v>676609</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="F91" t="n">
+        <v>116</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.7383</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.3108</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>670770</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="F92" t="n">
+        <v>118</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.1715</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>668709</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F93" t="n">
+        <v>15</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.6556999999999999</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.235</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="n">
+        <v>682829</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="F94" t="n">
+        <v>133</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.6982</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.2767</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" t="n">
+        <v>701398</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="F95" t="n">
+        <v>127</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.6676</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.2461</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" t="n">
+        <v>663993</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="F96" t="n">
+        <v>62</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.7029</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.2816</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>6</v>
+      </c>
+      <c r="D97" t="n">
+        <v>668715</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="F97" t="n">
+        <v>106</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.6556999999999999</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.235</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>7</v>
+      </c>
+      <c r="D98" t="n">
+        <v>663886</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="F98" t="n">
+        <v>80</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.5469000000000001</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.1503</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" t="n">
+        <v>666181</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="F99" t="n">
+        <v>49</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.4916</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.1122</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>9</v>
+      </c>
+      <c r="D100" t="n">
+        <v>663647</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="F100" t="n">
+        <v>84</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.0502</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>802139</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="F101" t="n">
+        <v>130</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.6215000000000001</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.2053</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>671056</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F102" t="n">
+        <v>120</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.6421</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.2228</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="n">
+        <v>676475</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="F103" t="n">
+        <v>129</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.6883</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.2665</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>4</v>
+      </c>
+      <c r="D104" t="n">
+        <v>691023</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="F104" t="n">
+        <v>127</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.7285</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.3101</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>5</v>
+      </c>
+      <c r="D105" t="n">
+        <v>669357</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="F105" t="n">
+        <v>112</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.1715</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" t="n">
+        <v>691026</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="F106" t="n">
+        <v>110</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.6791</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.2573</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>7</v>
+      </c>
+      <c r="D107" t="n">
+        <v>701675</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="F107" t="n">
+        <v>97</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.2184</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>8</v>
+      </c>
+      <c r="D108" t="n">
+        <v>686780</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="F108" t="n">
+        <v>73</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.1722</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>9</v>
+      </c>
+      <c r="D109" t="n">
+        <v>687363</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F109" t="n">
+        <v>84</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.08550000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -2127,7 +5372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2909,6 +6154,3477 @@
         <v>0.0086</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>680776</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F21" t="n">
+        <v>113</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0822</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>575929</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="F22" t="n">
+        <v>118</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.7284</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2593</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>701350</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="F23" t="n">
+        <v>108</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0929</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>596115</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>130</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4661</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>677800</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F25" t="n">
+        <v>124</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6939</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2235</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>678882</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="F26" t="n">
+        <v>106</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5595</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1213</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>691785</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="F27" t="n">
+        <v>86</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.1134</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>665966</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="F28" t="n">
+        <v>70</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.2263</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>655316</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F29" t="n">
+        <v>46</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.2419</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0927</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>663330</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="F30" t="n">
+        <v>38</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.3059</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.0268</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>663837</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="F31" t="n">
+        <v>70</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.0158</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>693307</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="F32" t="n">
+        <v>101</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>682985</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="F33" t="n">
+        <v>124</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.0334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>679529</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="F34" t="n">
+        <v>111</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.0309</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>672761</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="F35" t="n">
+        <v>56</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.0075</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>701678</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="F36" t="n">
+        <v>33</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.0168</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>690993</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F37" t="n">
+        <v>99</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.0129</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BOS@DET</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>670097</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0154</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>682818</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.0495</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>672960</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="F40" t="n">
+        <v>123</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.0771</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>665489</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="F41" t="n">
+        <v>126</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.1836</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.0619</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>660821</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="F42" t="n">
+        <v>104</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.0492</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>676391</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F43" t="n">
+        <v>134</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.0514</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>662139</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="F44" t="n">
+        <v>111</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.0529</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>664702</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="F45" t="n">
+        <v>51</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.0678</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>665926</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="F46" t="n">
+        <v>112</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.0346</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" t="n">
+        <v>678218</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="F47" t="n">
+        <v>44</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.0341</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>802415</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="F48" t="n">
+        <v>130</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.059</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>691406</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="F49" t="n">
+        <v>125</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.6345</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>668723</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="F50" t="n">
+        <v>40</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.0526</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>650490</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="F51" t="n">
+        <v>117</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.6345</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>666018</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="F52" t="n">
+        <v>119</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.1386</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>676356</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="F53" t="n">
+        <v>68</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.1341</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>810938</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="F54" t="n">
+        <v>86</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.0531</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" t="n">
+        <v>663743</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="F55" t="n">
+        <v>84</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.0468</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TOR@TB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>9</v>
+      </c>
+      <c r="D56" t="n">
+        <v>670764</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="F56" t="n">
+        <v>68</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.2201</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>607208</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F57" t="n">
+        <v>136</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.0479</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>656941</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="F58" t="n">
+        <v>123</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5903</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.1404</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="n">
+        <v>547180</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F59" t="n">
+        <v>125</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.5142</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.0968</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>666969</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F60" t="n">
+        <v>119</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.046</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>669016</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="F61" t="n">
+        <v>106</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.5262</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.1029</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>681082</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F62" t="n">
+        <v>97</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.0325</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" t="n">
+        <v>664761</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="F63" t="n">
+        <v>117</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>596117</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="F64" t="n">
+        <v>11</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.0404</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>9</v>
+      </c>
+      <c r="D65" t="n">
+        <v>702222</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="F65" t="n">
+        <v>97</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.0309</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>805300</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="F66" t="n">
+        <v>126</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.0326</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>669065</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="F67" t="n">
+        <v>46</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.0453</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="n">
+        <v>672640</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>132</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.6771</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.2077</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="n">
+        <v>669364</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="F69" t="n">
+        <v>125</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.6464</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.1814</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>689414</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F70" t="n">
+        <v>97</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.4818</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.2642</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" t="n">
+        <v>666624</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.5637</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.1238</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>8</v>
+      </c>
+      <c r="D72" t="n">
+        <v>683357</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="F72" t="n">
+        <v>92</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.0512</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PHI@MIA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9</v>
+      </c>
+      <c r="D73" t="n">
+        <v>688363</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="F73" t="n">
+        <v>70</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.0414</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>683002</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F74" t="n">
+        <v>139</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.0394</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
+        <v>668939</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="F75" t="n">
+        <v>71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.4441</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.0664</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" t="n">
+        <v>687637</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="F76" t="n">
+        <v>83</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.2244</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>624413</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="F77" t="n">
+        <v>126</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>694212</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F78" t="n">
+        <v>90</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.1244</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.0353</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>6</v>
+      </c>
+      <c r="D79" t="n">
+        <v>665750</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="F79" t="n">
+        <v>72</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.0322</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>7</v>
+      </c>
+      <c r="D80" t="n">
+        <v>681297</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="F80" t="n">
+        <v>60</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.0033</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" t="n">
+        <v>669236</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="F81" t="n">
+        <v>108</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" t="n">
+        <v>677942</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="F82" t="n">
+        <v>73</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.0021</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>663757</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="F83" t="n">
+        <v>105</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.2507</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.0977</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>592450</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="F84" t="n">
+        <v>121</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.8134</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.5958</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.3721</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>641355</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="F85" t="n">
+        <v>120</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.6858</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.2158</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>4</v>
+      </c>
+      <c r="D86" t="n">
+        <v>691176</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="F86" t="n">
+        <v>18</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.5914</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.1411</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>5</v>
+      </c>
+      <c r="D87" t="n">
+        <v>665862</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="F87" t="n">
+        <v>118</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.4836</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.2235</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.0825</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>6</v>
+      </c>
+      <c r="D88" t="n">
+        <v>502671</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="F88" t="n">
+        <v>35</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.1125</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>7</v>
+      </c>
+      <c r="D89" t="n">
+        <v>669224</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="F89" t="n">
+        <v>79</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.08110000000000001</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" t="n">
+        <v>641857</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F90" t="n">
+        <v>80</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.0421</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BAL@NYY</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>9</v>
+      </c>
+      <c r="D91" t="n">
+        <v>676609</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="F91" t="n">
+        <v>116</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.5195</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>670770</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="F92" t="n">
+        <v>118</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.0308</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>668709</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F93" t="n">
+        <v>15</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.4579</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.2031</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.0717</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="n">
+        <v>682829</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="F94" t="n">
+        <v>133</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.1551</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" t="n">
+        <v>701398</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="F95" t="n">
+        <v>127</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" t="n">
+        <v>663993</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="F96" t="n">
+        <v>62</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.6647</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.1968</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>6</v>
+      </c>
+      <c r="D97" t="n">
+        <v>668715</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F97" t="n">
+        <v>106</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.5044</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.2408</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.0921</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>7</v>
+      </c>
+      <c r="D98" t="n">
+        <v>663886</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="F98" t="n">
+        <v>80</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.1196</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.0334</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" t="n">
+        <v>666181</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="F99" t="n">
+        <v>49</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.0428</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CIN@CHC</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>9</v>
+      </c>
+      <c r="D100" t="n">
+        <v>663647</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F100" t="n">
+        <v>84</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.0041</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>802139</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="F101" t="n">
+        <v>130</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.0771</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>671056</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="F102" t="n">
+        <v>120</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.06710000000000001</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="n">
+        <v>676475</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="F103" t="n">
+        <v>129</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.5022</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>4</v>
+      </c>
+      <c r="D104" t="n">
+        <v>691023</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="F104" t="n">
+        <v>127</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.6311</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.1694</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>5</v>
+      </c>
+      <c r="D105" t="n">
+        <v>669357</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="F105" t="n">
+        <v>112</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.0458</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" t="n">
+        <v>691026</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="F106" t="n">
+        <v>110</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.0485</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>7</v>
+      </c>
+      <c r="D107" t="n">
+        <v>701675</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="F107" t="n">
+        <v>97</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.2088</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.0747</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>8</v>
+      </c>
+      <c r="D108" t="n">
+        <v>686780</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="F108" t="n">
+        <v>73</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.0434</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MIL@STL</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>9</v>
+      </c>
+      <c r="D109" t="n">
+        <v>687363</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="F109" t="n">
+        <v>84</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.0052</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
